--- a/public/downloads/kpi-dashboard.xlsx
+++ b/public/downloads/kpi-dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Explore Excel\Explore Excel Updated\explore-excel-complete\explore-excel\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D932251C-B7CA-4200-8F72-462870FC78AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7539CE3-EA14-4C83-AC37-52FB846903E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,11 +373,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5821,7 +5821,7 @@
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" s="16"/>
       <c r="B389" s="14" t="str">
-        <f t="shared" ref="B389:B452" si="6">IF(A389="","",TEXT(A389,"mmm"))</f>
+        <f t="shared" ref="B389:B404" si="6">IF(A389="","",TEXT(A389,"mmm"))</f>
         <v/>
       </c>
       <c r="C389" s="6"/>
@@ -6069,84 +6069,84 @@
       <c r="C2" s="26"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
     </row>
     <row r="5" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
     </row>
-    <row r="8" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+    <row r="8" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="30" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
     </row>
-    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="29"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="30" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="28" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="30" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
     </row>
-    <row r="17" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+    <row r="17" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="30" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="28" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="29"/>
@@ -6154,20 +6154,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
